--- a/survey_templates/050_nail_salon_customer_retention_survey--survey_templates.xlsx
+++ b/survey_templates/050_nail_salon_customer_retention_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1447,8 +1447,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option1':_'nail_service'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option1': 'nail_service'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1493,12 +1493,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option2':_'nail_extension'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option2': 'nail_extension'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1510,12 +1510,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option3':_'nail_painting'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option3': 'nail_painting'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option1':_'nail_service'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option1': 'nail_service'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1544,12 +1544,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option2':_'nail_extension'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option2': 'nail_extension'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option3':_'nail_painting'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option3': 'nail_painting'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1578,12 +1578,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option1':_'facebook'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option1': 'facebook'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1595,12 +1595,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option2':_'instagram'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option2': 'instagram'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1612,12 +1612,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option3':_'twitter'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option3': 'twitter'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1629,12 +1629,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option4':_'tiktok'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option4': 'tiktok'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option1':_'weekly'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option1': 'weekly'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option2':_'monthly'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option2': 'monthly'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option3':_'quarterly'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option3': 'quarterly'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option4':_'never'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option4': 'never'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1714,12 +1714,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option1':_'downtown'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option1': 'downtown'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1731,12 +1731,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option2':_'northside'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option2': 'northside'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'option3':_'other'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'option3': 'other'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1765,12 +1765,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'option1':_'morning'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'option1': 'morning'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1782,12 +1782,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'option2':_'afternoon'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'option2': 'afternoon'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1799,12 +1799,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'option3':_'evening'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'option3': 'evening'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1816,12 +1816,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'option1':_'satisfied'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'option1': 'satisfied'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1833,12 +1833,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'option2':_'neutral'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'option2': 'neutral'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1850,12 +1850,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'option3':_'dissatisfied'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'option3': 'dissatisfied'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'option1':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'option1': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1884,12 +1884,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'option2':_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'option2': False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
